--- a/src/legalizador_kit_contado/legalizador_kit_contado.xlsx
+++ b/src/legalizador_kit_contado/legalizador_kit_contado.xlsx
@@ -745,12 +745,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>* Su Solicitud fue enviada satisfactoriamente para el producto 270 y el MSISDN asignado es 3142481748.</t>
+          <t>Todos los campos obligatorios deben ser diligenciados</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>error</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>* Su Solicitud fue enviada satisfactoriamente para el producto 270 y el MSISDN asignado es 3142483033.</t>
+          <t>12877INV-021. El IMEI: "863015070094754", no pertenece al distribuidor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>* Su Solicitud fue enviada satisfactoriamente para el producto 270 y el MSISDN asignado es 3142485574.</t>
+          <t>12877INV-021. El IMEI: "865698070210849", no pertenece al distribuidor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>error</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>* Su Solicitud fue enviada satisfactoriamente para el producto 270 y el MSISDN asignado es 3142489353.</t>
+          <t>12877INV-021. El IMEI: "865785070131537", no pertenece al distribuidor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Procesado</t>
+          <t>error</t>
         </is>
       </c>
     </row>
